--- a/Starbucks_Hub_CMS.xlsx
+++ b/Starbucks_Hub_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C713AE54-F24F-4778-BC0E-811827C2643E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F510D533-0858-4349-B404-CA4372360CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -577,9 +577,6 @@
     <t>Nube Region CN</t>
   </si>
   <si>
-    <t>https://outlook.cloud.microsoft/host/377c982d-9686-450e-9a7c-22aeaf1bc162/7211f19f-262a-42eb-a02e-289956491741</t>
-  </si>
-  <si>
     <t>Okta</t>
   </si>
   <si>
@@ -1271,6 +1268,9 @@
   </si>
   <si>
     <t>Sistemas de Evidencias OPS</t>
+  </si>
+  <si>
+    <t>https://grupovips.sharepoint.com/:f:/r/sites/T_ReginSurResultadosPartner_Mexico/Shared%20Documents/General?d=wce8687e0e8754ef0bb6be053a26798c4&amp;csf=1&amp;web=1&amp;e=AM0oXr</t>
   </si>
 </sst>
 </file>
@@ -2083,7 +2083,7 @@
         <v>37</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>33</v>
@@ -3091,8 +3091,8 @@
       <c r="B35" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>177</v>
+      <c r="C35" s="16" t="s">
+        <v>408</v>
       </c>
       <c r="D35" s="13"/>
     </row>
@@ -3101,10 +3101,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>178</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>179</v>
       </c>
       <c r="D36" s="11"/>
     </row>
@@ -3113,10 +3113,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>180</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>181</v>
       </c>
       <c r="D37" s="13"/>
     </row>
@@ -3125,10 +3125,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>182</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>183</v>
       </c>
       <c r="D38" s="11"/>
     </row>
@@ -3137,10 +3137,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>184</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>185</v>
       </c>
       <c r="D39" s="13"/>
     </row>
@@ -3149,10 +3149,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="D40" s="11"/>
     </row>
@@ -3161,10 +3161,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>188</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>189</v>
       </c>
       <c r="D41" s="13"/>
     </row>
@@ -3173,10 +3173,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="D42" s="11"/>
     </row>
@@ -3185,10 +3185,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>192</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>193</v>
       </c>
       <c r="D43" s="13"/>
     </row>
@@ -3197,10 +3197,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>194</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>195</v>
       </c>
       <c r="D44" s="11"/>
     </row>
@@ -3209,10 +3209,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>196</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>197</v>
       </c>
       <c r="D45" s="13"/>
     </row>
@@ -3221,10 +3221,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>198</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>199</v>
       </c>
       <c r="D46" s="11"/>
     </row>
@@ -3233,13 +3233,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="D47" s="13" t="s">
         <v>201</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="46" customHeight="1">
@@ -3247,10 +3247,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" s="16" t="s">
         <v>203</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>204</v>
       </c>
       <c r="D48" s="11"/>
     </row>
@@ -3259,13 +3259,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="D49" s="13" t="s">
         <v>206</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="32" customHeight="1">
@@ -3273,14 +3273,17 @@
         <v>49</v>
       </c>
       <c r="B50" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C50" s="17" t="s">
-        <v>209</v>
-      </c>
       <c r="D50" s="12"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C35" r:id="rId1" xr:uid="{ECF64753-365D-4D6E-AD6A-BE72448D5039}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3307,45 +3310,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="46" customHeight="1">
       <c r="A2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="D2" s="27">
         <v>46218</v>
@@ -3354,19 +3357,19 @@
         <v>46219</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>84</v>
@@ -3374,13 +3377,13 @@
     </row>
     <row r="3" spans="1:11" ht="46" customHeight="1">
       <c r="A3" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>227</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>228</v>
       </c>
       <c r="D3" s="28">
         <v>46231</v>
@@ -3389,31 +3392,31 @@
         <v>46231</v>
       </c>
       <c r="F3" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I3" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="15"/>
       <c r="K3" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="46" customHeight="1">
       <c r="A4" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="D4" s="29">
         <v>46235</v>
@@ -3422,13 +3425,13 @@
         <v>46239</v>
       </c>
       <c r="F4" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I4" s="20" t="s">
         <v>17</v>
@@ -3437,18 +3440,18 @@
         <v>161</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="46" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>234</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>235</v>
       </c>
       <c r="D5" s="28">
         <v>46236</v>
@@ -3457,19 +3460,19 @@
         <v>46237</v>
       </c>
       <c r="F5" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I5" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>84</v>
@@ -3477,13 +3480,13 @@
     </row>
     <row r="6" spans="1:11" ht="46" customHeight="1">
       <c r="A6" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>237</v>
       </c>
       <c r="D6" s="29">
         <v>46250</v>
@@ -3492,19 +3495,19 @@
         <v>46251</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="H6" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I6" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>84</v>
@@ -3512,13 +3515,13 @@
     </row>
     <row r="7" spans="1:11" ht="46" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="13" t="s">
         <v>239</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>240</v>
       </c>
       <c r="D7" s="28">
         <v>46259</v>
@@ -3527,13 +3530,13 @@
         <v>46259</v>
       </c>
       <c r="F7" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="H7" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I7" s="19" t="s">
         <v>17</v>
@@ -3545,13 +3548,13 @@
     </row>
     <row r="8" spans="1:11" ht="46" customHeight="1">
       <c r="A8" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>241</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>242</v>
       </c>
       <c r="D8" s="29">
         <v>46265</v>
@@ -3560,19 +3563,19 @@
         <v>46266</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="H8" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>84</v>
@@ -3580,13 +3583,13 @@
     </row>
     <row r="9" spans="1:11" ht="46" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>231</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>232</v>
       </c>
       <c r="D9" s="28">
         <v>46266</v>
@@ -3595,13 +3598,13 @@
         <v>46270</v>
       </c>
       <c r="F9" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I9" s="19" t="s">
         <v>17</v>
@@ -3610,18 +3613,18 @@
         <v>161</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="46" customHeight="1">
       <c r="A10" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>244</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="D10" s="29">
         <v>46281</v>
@@ -3630,19 +3633,19 @@
         <v>46282</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="H10" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I10" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>84</v>
@@ -3650,13 +3653,13 @@
     </row>
     <row r="11" spans="1:11" ht="46" customHeight="1">
       <c r="A11" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="D11" s="28">
         <v>46295</v>
@@ -3665,19 +3668,19 @@
         <v>46296</v>
       </c>
       <c r="F11" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="H11" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I11" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K11" s="13" t="s">
         <v>84</v>
@@ -3685,13 +3688,13 @@
     </row>
     <row r="12" spans="1:11" ht="46" customHeight="1">
       <c r="A12" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="11" t="s">
         <v>249</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>250</v>
       </c>
       <c r="D12" s="29">
         <v>46296</v>
@@ -3700,33 +3703,33 @@
         <v>46305</v>
       </c>
       <c r="F12" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="H12" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I12" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="K12" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="46" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>231</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>232</v>
       </c>
       <c r="D13" s="28">
         <v>46296</v>
@@ -3735,13 +3738,13 @@
         <v>46300</v>
       </c>
       <c r="F13" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="H13" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I13" s="19" t="s">
         <v>17</v>
@@ -3750,18 +3753,18 @@
         <v>161</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="46" customHeight="1">
       <c r="A14" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>254</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>255</v>
       </c>
       <c r="D14" s="29">
         <v>46310</v>
@@ -3770,19 +3773,19 @@
         <v>46311</v>
       </c>
       <c r="F14" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="H14" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I14" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>84</v>
@@ -3790,13 +3793,13 @@
     </row>
     <row r="15" spans="1:11" ht="46" customHeight="1">
       <c r="A15" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>257</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>258</v>
       </c>
       <c r="D15" s="28">
         <v>46322</v>
@@ -3805,31 +3808,31 @@
         <v>46322</v>
       </c>
       <c r="F15" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I15" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="46" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="D16" s="29">
         <v>46327</v>
@@ -3838,13 +3841,13 @@
         <v>46331</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="H16" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I16" s="20" t="s">
         <v>17</v>
@@ -3853,18 +3856,18 @@
         <v>161</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="46" customHeight="1">
       <c r="A17" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>261</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>262</v>
       </c>
       <c r="D17" s="28">
         <v>46328</v>
@@ -3873,19 +3876,19 @@
         <v>46329</v>
       </c>
       <c r="F17" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="H17" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>84</v>
@@ -3893,13 +3896,13 @@
     </row>
     <row r="18" spans="1:11" ht="46" customHeight="1">
       <c r="A18" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="D18" s="29">
         <v>46342</v>
@@ -3908,19 +3911,19 @@
         <v>46343</v>
       </c>
       <c r="F18" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G18" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="H18" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I18" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>84</v>
@@ -3928,13 +3931,13 @@
     </row>
     <row r="19" spans="1:11" ht="46" customHeight="1">
       <c r="A19" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>265</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>266</v>
       </c>
       <c r="D19" s="28">
         <v>46356</v>
@@ -3943,19 +3946,19 @@
         <v>46357</v>
       </c>
       <c r="F19" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I19" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K19" s="13" t="s">
         <v>84</v>
@@ -3963,13 +3966,13 @@
     </row>
     <row r="20" spans="1:11" ht="46" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="D20" s="29">
         <v>46357</v>
@@ -3978,13 +3981,13 @@
         <v>46361</v>
       </c>
       <c r="F20" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G20" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="H20" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="I20" s="20" t="s">
         <v>17</v>
@@ -3993,18 +3996,18 @@
         <v>161</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="46" customHeight="1">
       <c r="A21" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>268</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>269</v>
       </c>
       <c r="D21" s="30">
         <v>46371</v>
@@ -4013,19 +4016,19 @@
         <v>46372</v>
       </c>
       <c r="F21" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="G21" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="H21" s="26" t="s">
         <v>223</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>224</v>
       </c>
       <c r="I21" s="31" t="s">
         <v>17</v>
       </c>
       <c r="J21" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K21" s="26" t="s">
         <v>84</v>
@@ -4071,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>7</v>
@@ -4083,7 +4086,7 @@
         <v>8</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="46" customHeight="1">
@@ -4091,20 +4094,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>274</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>275</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="H2" s="14"/>
     </row>
@@ -4113,23 +4116,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="32" customHeight="1">
@@ -4137,23 +4140,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>281</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>282</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="16" t="s">
         <v>284</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46" customHeight="1">
@@ -4161,20 +4164,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>287</v>
-      </c>
       <c r="D5" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H5" s="15"/>
     </row>
@@ -4183,20 +4186,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>290</v>
-      </c>
       <c r="D6" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="s">
         <v>84</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H6" s="16"/>
     </row>
@@ -4205,20 +4208,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>292</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>293</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H7" s="15"/>
     </row>
@@ -4227,20 +4230,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="11" t="s">
         <v>296</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>297</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H8" s="16"/>
     </row>
@@ -4249,20 +4252,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>300</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>301</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>302</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>303</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>98</v>
@@ -4273,20 +4276,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>305</v>
-      </c>
       <c r="D10" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H10" s="16"/>
     </row>
@@ -4295,20 +4298,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
         <v>308</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>309</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H11" s="15"/>
     </row>
@@ -4317,20 +4320,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>311</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>312</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4367,7 +4370,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -4393,13 +4396,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="14" t="s">
         <v>316</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>317</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>13</v>
@@ -4408,7 +4411,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>15</v>
@@ -4425,13 +4428,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>320</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>321</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>13</v>
@@ -4440,13 +4443,13 @@
         <v>1</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>322</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>323</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>17</v>
@@ -4457,13 +4460,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="16" t="s">
         <v>325</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>326</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>13</v>
@@ -4472,13 +4475,13 @@
         <v>2</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>328</v>
-      </c>
       <c r="I4" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J4" s="20" t="s">
         <v>17</v>
@@ -4489,13 +4492,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="15" t="s">
         <v>330</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>331</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>13</v>
@@ -4507,10 +4510,10 @@
         <v>14</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>17</v>
@@ -4521,13 +4524,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="16" t="s">
         <v>334</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>335</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>13</v>
@@ -4536,13 +4539,13 @@
         <v>2</v>
       </c>
       <c r="G6" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>337</v>
-      </c>
       <c r="I6" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J6" s="20" t="s">
         <v>17</v>
@@ -4553,10 +4556,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>338</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>339</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>121</v>
@@ -4571,10 +4574,10 @@
         <v>14</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>17</v>
@@ -4585,13 +4588,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="17" t="s">
         <v>342</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>343</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>13</v>
@@ -4603,10 +4606,10 @@
         <v>14</v>
       </c>
       <c r="H8" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>344</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>345</v>
       </c>
       <c r="J8" s="21" t="s">
         <v>17</v>
@@ -4644,19 +4647,19 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="46" customHeight="1">
@@ -4664,19 +4667,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>350</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="46" customHeight="1">
@@ -4684,19 +4687,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>354</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
@@ -4704,19 +4707,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>357</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="46" customHeight="1">
@@ -4724,19 +4727,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>361</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="46" customHeight="1">
@@ -4744,19 +4747,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>364</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="46" customHeight="1">
@@ -4764,19 +4767,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>367</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="46" customHeight="1">
@@ -4784,19 +4787,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>370</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -4821,22 +4824,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>9</v>
@@ -4847,150 +4850,150 @@
     </row>
     <row r="2" spans="1:8" ht="32" customHeight="1">
       <c r="A2" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>379</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>380</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" customHeight="1">
       <c r="A3" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>384</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>385</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="32" customHeight="1">
       <c r="A4" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>389</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="32" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>394</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>395</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="32" customHeight="1">
       <c r="A6" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>400</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>401</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="32" customHeight="1">
       <c r="A7" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>403</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>378</v>
-      </c>
-      <c r="C7" s="26" t="s">
+      <c r="D7" s="26" t="s">
         <v>404</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>405</v>
       </c>
       <c r="E7" s="26"/>
       <c r="F7" s="26" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G7" s="31" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/Starbucks_Hub_CMS.xlsx
+++ b/Starbucks_Hub_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F510D533-0858-4349-B404-CA4372360CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB59F42-91CC-48EC-8FB0-953EB314D0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -349,15 +349,6 @@
     <t>💵</t>
   </si>
   <si>
-    <t>Boost CN</t>
-  </si>
-  <si>
-    <t>https://sbx-mex.github.io/Boost_CN/</t>
-  </si>
-  <si>
-    <t>Seguimiento a Impulso items Centro Norte</t>
-  </si>
-  <si>
     <t>📍</t>
   </si>
   <si>
@@ -1271,6 +1262,15 @@
   </si>
   <si>
     <t>https://grupovips.sharepoint.com/:f:/r/sites/T_ReginSurResultadosPartner_Mexico/Shared%20Documents/General?d=wce8687e0e8754ef0bb6be053a26798c4&amp;csf=1&amp;web=1&amp;e=AM0oXr</t>
+  </si>
+  <si>
+    <t>Control Ops 360°</t>
+  </si>
+  <si>
+    <t>Multiherramienta Operativa</t>
+  </si>
+  <si>
+    <t>https://sbx-mex.github.io/ControlOps-360/</t>
   </si>
 </sst>
 </file>
@@ -2083,7 +2083,7 @@
         <v>37</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>33</v>
@@ -2589,25 +2589,25 @@
         <v>29</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>100</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>102</v>
+        <v>408</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>103</v>
+        <v>407</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="J19" s="23">
         <v>18</v>
@@ -2624,19 +2624,19 @@
         <v>36</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I20" s="21" t="s">
         <v>56</v>
@@ -2650,7 +2650,7 @@
     <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Si"/>
     <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" sqref="I2:I20" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
@@ -2689,10 +2689,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D2" s="10"/>
     </row>
@@ -2701,10 +2701,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D3" s="13"/>
     </row>
@@ -2713,10 +2713,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D4" s="11"/>
     </row>
@@ -2725,10 +2725,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D5" s="13"/>
     </row>
@@ -2737,10 +2737,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D6" s="11"/>
     </row>
@@ -2749,10 +2749,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" s="13"/>
     </row>
@@ -2761,10 +2761,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -2773,10 +2773,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D9" s="13"/>
     </row>
@@ -2785,10 +2785,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D10" s="11"/>
     </row>
@@ -2797,10 +2797,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D11" s="13"/>
     </row>
@@ -2809,10 +2809,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" s="11"/>
     </row>
@@ -2821,10 +2821,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D13" s="13"/>
     </row>
@@ -2833,10 +2833,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D14" s="11"/>
     </row>
@@ -2845,10 +2845,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D15" s="13"/>
     </row>
@@ -2857,10 +2857,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D16" s="11"/>
     </row>
@@ -2869,10 +2869,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D17" s="13"/>
     </row>
@@ -2881,10 +2881,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D18" s="11"/>
     </row>
@@ -2893,10 +2893,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D19" s="13"/>
     </row>
@@ -2905,10 +2905,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D20" s="11"/>
     </row>
@@ -2917,10 +2917,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D21" s="13"/>
     </row>
@@ -2929,10 +2929,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D22" s="11"/>
     </row>
@@ -2941,10 +2941,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D23" s="13"/>
     </row>
@@ -2953,10 +2953,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D24" s="11"/>
     </row>
@@ -2965,13 +2965,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="46" customHeight="1">
@@ -2979,13 +2979,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="32" customHeight="1">
@@ -2993,10 +2993,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D27" s="13"/>
     </row>
@@ -3005,10 +3005,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D28" s="11"/>
     </row>
@@ -3017,10 +3017,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D29" s="13"/>
     </row>
@@ -3029,10 +3029,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D30" s="11"/>
     </row>
@@ -3041,10 +3041,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D31" s="13"/>
     </row>
@@ -3053,10 +3053,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D32" s="11"/>
     </row>
@@ -3065,10 +3065,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D33" s="13"/>
     </row>
@@ -3077,10 +3077,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D34" s="11"/>
     </row>
@@ -3089,10 +3089,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D35" s="13"/>
     </row>
@@ -3101,10 +3101,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D36" s="11"/>
     </row>
@@ -3113,10 +3113,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D37" s="13"/>
     </row>
@@ -3125,10 +3125,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D38" s="11"/>
     </row>
@@ -3137,10 +3137,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D39" s="13"/>
     </row>
@@ -3149,10 +3149,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D40" s="11"/>
     </row>
@@ -3161,10 +3161,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D41" s="13"/>
     </row>
@@ -3173,10 +3173,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D42" s="11"/>
     </row>
@@ -3185,10 +3185,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D43" s="13"/>
     </row>
@@ -3197,10 +3197,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D44" s="11"/>
     </row>
@@ -3209,10 +3209,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D45" s="13"/>
     </row>
@@ -3221,10 +3221,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D46" s="11"/>
     </row>
@@ -3233,13 +3233,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="46" customHeight="1">
@@ -3247,10 +3247,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D48" s="11"/>
     </row>
@@ -3259,13 +3259,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="32" customHeight="1">
@@ -3273,10 +3273,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D50" s="12"/>
     </row>
@@ -3310,45 +3310,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="46" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D2" s="27">
         <v>46218</v>
@@ -3357,19 +3357,19 @@
         <v>46219</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>84</v>
@@ -3377,13 +3377,13 @@
     </row>
     <row r="3" spans="1:11" ht="46" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D3" s="28">
         <v>46231</v>
@@ -3392,31 +3392,31 @@
         <v>46231</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I3" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="15"/>
       <c r="K3" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="46" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D4" s="29">
         <v>46235</v>
@@ -3425,33 +3425,33 @@
         <v>46239</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I4" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="46" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D5" s="28">
         <v>46236</v>
@@ -3460,19 +3460,19 @@
         <v>46237</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I5" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>84</v>
@@ -3480,13 +3480,13 @@
     </row>
     <row r="6" spans="1:11" ht="46" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D6" s="29">
         <v>46250</v>
@@ -3495,19 +3495,19 @@
         <v>46251</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I6" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>84</v>
@@ -3515,13 +3515,13 @@
     </row>
     <row r="7" spans="1:11" ht="46" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D7" s="28">
         <v>46259</v>
@@ -3530,13 +3530,13 @@
         <v>46259</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I7" s="19" t="s">
         <v>17</v>
@@ -3548,13 +3548,13 @@
     </row>
     <row r="8" spans="1:11" ht="46" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D8" s="29">
         <v>46265</v>
@@ -3563,19 +3563,19 @@
         <v>46266</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>84</v>
@@ -3583,13 +3583,13 @@
     </row>
     <row r="9" spans="1:11" ht="46" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D9" s="28">
         <v>46266</v>
@@ -3598,33 +3598,33 @@
         <v>46270</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I9" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="46" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D10" s="29">
         <v>46281</v>
@@ -3633,19 +3633,19 @@
         <v>46282</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I10" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>84</v>
@@ -3653,13 +3653,13 @@
     </row>
     <row r="11" spans="1:11" ht="46" customHeight="1">
       <c r="A11" s="13" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D11" s="28">
         <v>46295</v>
@@ -3668,19 +3668,19 @@
         <v>46296</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I11" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K11" s="13" t="s">
         <v>84</v>
@@ -3688,13 +3688,13 @@
     </row>
     <row r="12" spans="1:11" ht="46" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D12" s="29">
         <v>46296</v>
@@ -3703,33 +3703,33 @@
         <v>46305</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I12" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="46" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D13" s="28">
         <v>46296</v>
@@ -3738,33 +3738,33 @@
         <v>46300</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I13" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="46" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D14" s="29">
         <v>46310</v>
@@ -3773,19 +3773,19 @@
         <v>46311</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I14" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>84</v>
@@ -3793,13 +3793,13 @@
     </row>
     <row r="15" spans="1:11" ht="46" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D15" s="28">
         <v>46322</v>
@@ -3808,31 +3808,31 @@
         <v>46322</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I15" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="46" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D16" s="29">
         <v>46327</v>
@@ -3841,33 +3841,33 @@
         <v>46331</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I16" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="46" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D17" s="28">
         <v>46328</v>
@@ -3876,19 +3876,19 @@
         <v>46329</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>84</v>
@@ -3896,13 +3896,13 @@
     </row>
     <row r="18" spans="1:11" ht="46" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D18" s="29">
         <v>46342</v>
@@ -3911,19 +3911,19 @@
         <v>46343</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I18" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>84</v>
@@ -3931,13 +3931,13 @@
     </row>
     <row r="19" spans="1:11" ht="46" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D19" s="28">
         <v>46356</v>
@@ -3946,19 +3946,19 @@
         <v>46357</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I19" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K19" s="13" t="s">
         <v>84</v>
@@ -3966,13 +3966,13 @@
     </row>
     <row r="20" spans="1:11" ht="46" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D20" s="29">
         <v>46357</v>
@@ -3981,33 +3981,33 @@
         <v>46361</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I20" s="20" t="s">
         <v>17</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="46" customHeight="1">
       <c r="A21" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D21" s="30">
         <v>46371</v>
@@ -4016,19 +4016,19 @@
         <v>46372</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I21" s="31" t="s">
         <v>17</v>
       </c>
       <c r="J21" s="32" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K21" s="26" t="s">
         <v>84</v>
@@ -4074,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>7</v>
@@ -4086,7 +4086,7 @@
         <v>8</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="46" customHeight="1">
@@ -4094,20 +4094,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H2" s="14"/>
     </row>
@@ -4116,23 +4116,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="32" customHeight="1">
@@ -4140,23 +4140,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46" customHeight="1">
@@ -4164,20 +4164,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H5" s="15"/>
     </row>
@@ -4186,20 +4186,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="s">
         <v>84</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H6" s="16"/>
     </row>
@@ -4208,20 +4208,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H7" s="15"/>
     </row>
@@ -4230,20 +4230,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H8" s="16"/>
     </row>
@@ -4252,20 +4252,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="13" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>98</v>
@@ -4276,20 +4276,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H10" s="16"/>
     </row>
@@ -4298,20 +4298,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H11" s="15"/>
     </row>
@@ -4320,20 +4320,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4370,7 +4370,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -4396,13 +4396,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>13</v>
@@ -4411,7 +4411,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>15</v>
@@ -4428,13 +4428,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>13</v>
@@ -4443,13 +4443,13 @@
         <v>1</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>17</v>
@@ -4460,13 +4460,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>13</v>
@@ -4475,13 +4475,13 @@
         <v>2</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="J4" s="20" t="s">
         <v>17</v>
@@ -4492,13 +4492,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>13</v>
@@ -4510,10 +4510,10 @@
         <v>14</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>17</v>
@@ -4524,13 +4524,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>13</v>
@@ -4539,13 +4539,13 @@
         <v>2</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J6" s="20" t="s">
         <v>17</v>
@@ -4556,13 +4556,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>13</v>
@@ -4574,10 +4574,10 @@
         <v>14</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>17</v>
@@ -4588,13 +4588,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>13</v>
@@ -4606,10 +4606,10 @@
         <v>14</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J8" s="21" t="s">
         <v>17</v>
@@ -4647,19 +4647,19 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="46" customHeight="1">
@@ -4667,19 +4667,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="46" customHeight="1">
@@ -4687,19 +4687,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
@@ -4707,19 +4707,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="46" customHeight="1">
@@ -4727,19 +4727,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="46" customHeight="1">
@@ -4747,19 +4747,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="46" customHeight="1">
@@ -4767,19 +4767,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="46" customHeight="1">
@@ -4787,19 +4787,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -4824,22 +4824,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>9</v>
@@ -4850,150 +4850,150 @@
     </row>
     <row r="2" spans="1:8" ht="32" customHeight="1">
       <c r="A2" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>376</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>379</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="32" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="32" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>391</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>394</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="32" customHeight="1">
       <c r="A6" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>397</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>398</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>400</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="32" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E7" s="26"/>
       <c r="F7" s="26" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G7" s="31" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
